--- a/figure4/figure4B-C.Each_type_stimulation/plotting/data/Labellar_candidate_stimulation_SEM.xlsx
+++ b/figure4/figure4B-C.Each_type_stimulation/plotting/data/Labellar_candidate_stimulation_SEM.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>0Hz</t>
@@ -488,161 +493,161 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>high_salt</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02376446927663229</v>
+        <v>0.05703288525052892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1974202370579065</v>
+        <v>0.2278618002210989</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2206869955389306</v>
+        <v>0.2935723931162465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1857417562100671</v>
+        <v>0.3113936415535808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.187922191345248</v>
+        <v>0.3349388003800097</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1973296733894829</v>
+        <v>0.3549563353428136</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2088875295464045</v>
+        <v>0.3377928359216636</v>
       </c>
       <c r="J2" t="n">
-        <v>0.151868364052557</v>
+        <v>0.3352968833735261</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1625699849295681</v>
+        <v>0.4251526196555774</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1720254341659977</v>
+        <v>0.3453983207834109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05703288525052892</v>
+        <v>0.07024243731534378</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2278618002210989</v>
+        <v>0.2988963030885461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2935723931162465</v>
+        <v>0.3831223694852599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3113936415535808</v>
+        <v>0.4444465659671588</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3349388003800097</v>
+        <v>0.4304602188356085</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3549563353428136</v>
+        <v>0.3875470939124689</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3377928359216636</v>
+        <v>0.4289204471694023</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3352968833735261</v>
+        <v>0.4441103466482176</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4251526196555774</v>
+        <v>0.5361725468540888</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3453983207834109</v>
+        <v>0.4831811254591802</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07024243731534378</v>
+        <v>0.3350264914898522</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2988963030885461</v>
+        <v>0.3645545226711637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3831223694852599</v>
+        <v>0.3618739421400773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4444465659671588</v>
+        <v>0.3953112697609316</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4304602188356085</v>
+        <v>0.3696741808674228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3875470939124689</v>
+        <v>0.4323493957437664</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4289204471694023</v>
+        <v>0.421978672446843</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4441103466482176</v>
+        <v>0.3794005139690773</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5361725468540888</v>
+        <v>0.4151493707089052</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4831811254591802</v>
+        <v>0.3804786459185325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>high_salt</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3350264914898522</v>
+        <v>0.02376446927663229</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3645545226711637</v>
+        <v>0.1974202370579065</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3618739421400773</v>
+        <v>0.2206869955389306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3953112697609316</v>
+        <v>0.1857417562100671</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3696741808674228</v>
+        <v>0.187922191345248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4323493957437664</v>
+        <v>0.1973296733894829</v>
       </c>
       <c r="I5" t="n">
-        <v>0.421978672446843</v>
+        <v>0.2088875295464045</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3794005139690773</v>
+        <v>0.151868364052557</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4151493707089052</v>
+        <v>0.1625699849295681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3804786459185325</v>
+        <v>0.1720254341659977</v>
       </c>
     </row>
     <row r="6">
